--- a/artfynd/A 34201-2020 artfynd.xlsx
+++ b/artfynd/A 34201-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34201-2020 artfynd.xlsx
+++ b/artfynd/A 34201-2020 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676830</v>
+        <v>118676831</v>
       </c>
       <c r="B3" t="n">
-        <v>96807</v>
+        <v>97763</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400617</v>
+        <v>400583</v>
       </c>
       <c r="R3" t="n">
-        <v>6854300</v>
+        <v>6854330</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676831</v>
+        <v>118676830</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
+        <v>96807</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400583</v>
+        <v>400617</v>
       </c>
       <c r="R4" t="n">
-        <v>6854330</v>
+        <v>6854300</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 34201-2020 artfynd.xlsx
+++ b/artfynd/A 34201-2020 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676831</v>
+        <v>118676830</v>
       </c>
       <c r="B3" t="n">
-        <v>97763</v>
+        <v>96814</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400583</v>
+        <v>400617</v>
       </c>
       <c r="R3" t="n">
-        <v>6854330</v>
+        <v>6854300</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676830</v>
+        <v>118676831</v>
       </c>
       <c r="B4" t="n">
-        <v>96807</v>
+        <v>97770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400617</v>
+        <v>400583</v>
       </c>
       <c r="R4" t="n">
-        <v>6854300</v>
+        <v>6854330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 34201-2020 artfynd.xlsx
+++ b/artfynd/A 34201-2020 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676830</v>
+        <v>118676831</v>
       </c>
       <c r="B3" t="n">
-        <v>96814</v>
+        <v>97770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>400617</v>
+        <v>400583</v>
       </c>
       <c r="R3" t="n">
-        <v>6854300</v>
+        <v>6854330</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676831</v>
+        <v>118676830</v>
       </c>
       <c r="B4" t="n">
-        <v>97770</v>
+        <v>96814</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>400583</v>
+        <v>400617</v>
       </c>
       <c r="R4" t="n">
-        <v>6854330</v>
+        <v>6854300</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
